--- a/data/experiments/EXPERIMENT-02-results.xlsx
+++ b/data/experiments/EXPERIMENT-02-results.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Deflection</t>
+          <t>Self-service</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Deflection at or above 35%</t>
+          <t>Self-service at or above 35%</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
